--- a/config/rules/CRS610MI.xlsx
+++ b/config/rules/CRS610MI.xlsx
@@ -1273,14 +1273,9 @@
           <t>AGCH</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AGCH</t>
-        </is>
-      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1366,14 +1361,9 @@
           <t>AGCT</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AGCT</t>
-        </is>
-      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2119,14 +2109,9 @@
           <t>BPCD</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>BPCD</t>
-        </is>
-      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2767,12 +2752,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>MAP</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>translation_tbl\OCUSMA_CSCD_Country.xlsx|MOVEX|M3</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2900,9 +2880,14 @@
           <t>CUA3</t>
         </is>
       </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CUA3</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>IGNORE</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2940,9 +2925,14 @@
           <t>CUA4</t>
         </is>
       </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CUA4</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>IGNORE</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3025,14 +3015,9 @@
           <t>CUCL</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>CUCL</t>
-        </is>
-      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3255,14 +3240,9 @@
           <t>CUSU</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>CUSU</t>
-        </is>
-      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3300,14 +3280,14 @@
           <t>CUTP</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>CUTP</t>
-        </is>
-      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>CONST</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3348,21 +3328,14 @@
           <t>DESV</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>LHCD</t>
-        </is>
-      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>PYTHON</t>
+          <t>CONST</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>if source == 'SP':
-    return 'ES'
-return source</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3658,14 +3631,9 @@
           <t>EALO</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>EALO</t>
-        </is>
-      </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3713,14 +3681,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>PYTHON</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>if source == 'PQ':
-    return 'QC'
-return source</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4481,14 +4442,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>PYTHON</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>if source == 'SP':
-    return 'ES'
-return source</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4558,14 +4512,9 @@
           <t>MEAL</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>MEAL</t>
-        </is>
-      </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4648,14 +4597,9 @@
           <t>MTIC</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>MTIC</t>
-        </is>
-      </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4840,14 +4784,9 @@
           <t>OREF</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>OREF</t>
-        </is>
-      </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4892,12 +4831,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>MAP</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>translation_tbl\OCUSMA_ORTP_OrderTypes.xlsx|MOVEX|M3</t>
+          <t>DIRECT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5384,14 +5318,9 @@
           <t>PWMT</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>PWMT</t>
-        </is>
-      </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5617,14 +5546,9 @@
           <t>RASN</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>RASN</t>
-        </is>
-      </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>DIRECT</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -10180,7 +10104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -11416,6 +11340,579 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-17 15:37:23</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CUA3</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Type: IGNORE-&gt;DIRECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-17 15:37:27</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CUA4</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Type: IGNORE-&gt;DIRECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-17 15:37:40</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CUA3</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Src: -&gt;CUA3</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-17 15:37:45</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CUA4</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Src: -&gt;CUA4</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-17 15:38:04</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>CUTP</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Type: DIRECT-&gt;CONST, Src: CUTP-&gt;, Val: ''-&gt;'0'</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-17 15:39:51</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CUSU</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Type: DIRECT-&gt;IGNORE, Src: CUSU-&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:12:53</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CSCD</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Type: MAP-&gt;DIRECT, Val: 'translation_tbl\OCUSMA_CSCD_Country.xlsx|MOVEX|M3'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:13:04</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LHCD</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Type: PYTHON-&gt;DIRECT, Val: 'if source == 'SP':
+    return 'ES'
+return source'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:13:41</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>MEAL</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Type: DIRECT-&gt;IGNORE, Src: MEAL-&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:17:03</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>EALO</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Type: DIRECT-&gt;IGNORE, Src: EALO-&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:17:16</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ECAR</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Type: PYTHON-&gt;DIRECT, Val: 'if source == 'PQ':
+    return 'QC'
+return source'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:17:36</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>DESV</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Type: PYTHON-&gt;CONST, Src: LHCD-&gt;, Val: 'if source == 'SP':
+    return 'ES'
+return source'-&gt;'GB'</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:18:36</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>RASN</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Type: DIRECT-&gt;IGNORE, Src: RASN-&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:19:15</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>CUCL</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Type: DIRECT-&gt;IGNORE, Src: CUCL-&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:19:31</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>OREF</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Type: DIRECT-&gt;IGNORE, Src: OREF-&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:20:14</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ORTP</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Type: MAP-&gt;DIRECT, Val: 'translation_tbl\OCUSMA_ORTP_OrderTypes.xlsx|MOVEX|M3'-&gt;''</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:21:02</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AGCH</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Type: DIRECT-&gt;IGNORE, Src: AGCH-&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:21:16</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AGCT</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Type: DIRECT-&gt;IGNORE, Src: AGCT-&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:21:26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>MTIC</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Type: DIRECT-&gt;IGNORE, Src: MTIC-&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:21:38</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>PWMT</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Type: DIRECT-&gt;IGNORE, Src: PWMT-&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:21:50</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>w10itasv</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>BPCD</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Type: DIRECT-&gt;IGNORE, Src: BPCD-&gt;</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
